--- a/data/employees/EMP093/AST-EMP093-06.xlsx
+++ b/data/employees/EMP093/AST-EMP093-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Taylor Miller (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Senior Engineer | Location: Austin | Date: 2025-04-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP093</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+        <v>83</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP093</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>76</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP093</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>74</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP093</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>67</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>61</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>86</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>67</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>88</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>64</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>79</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>99</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>88</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>97</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>76</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>69</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>63</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>79</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>95</v>
       </c>
-      <c r="F8" t="n">
-        <v>340</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp093 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>88</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP093</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP093 contributes to ast emp093 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>